--- a/Data/static2.xlsx
+++ b/Data/static2.xlsx
@@ -11369,10 +11369,10 @@
         <v>98.68</v>
       </c>
       <c r="C784" t="str">
-        <v>2760.32</v>
+        <v>590.8</v>
       </c>
       <c r="D784" t="str">
-        <v>1079.74</v>
+        <v>1135.08</v>
       </c>
     </row>
     <row r="785">
